--- a/excel-theme/examples/preview_dcf-valuation.xlsx
+++ b/excel-theme/examples/preview_dcf-valuation.xlsx
@@ -170,7 +170,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -489,11 +489,10 @@
     <col width="9" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>비품 구매 내역 (합계 없음)</t>
+          <t>01_단순표</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -592,11 +591,10 @@
     <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>결산 마감 진척 현황</t>
+          <t>10_날짜_진척_상태</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -721,11 +719,10 @@
     <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>KPI 달성률 (90% 미만 강조)</t>
+          <t>11_KPI_조건부강조</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -827,11 +824,10 @@
     <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>헤더 3종 — 제목 / 본문 기본 / 본문 세컨더리</t>
+          <t>헤더3종_데모</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -964,11 +960,10 @@
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>부서별 경비 (합계만)</t>
+          <t>02_합계만</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -1100,11 +1095,10 @@
     <col width="9" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>손익 요약 (소계 + 합계)</t>
+          <t>03_소계_합계</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -1233,11 +1227,10 @@
     <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>현금흐름 (섹션 + 소계 + 합계)</t>
+          <t>04_섹션_소계_합계</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -1378,11 +1371,10 @@
     <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>분기별 실적 (묶음 헤더)</t>
+          <t>05_묶음헤더</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -1520,11 +1512,10 @@
     <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>지역별 매출 및 비중</t>
+          <t>06_와이드_퍼센트</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -1696,11 +1687,10 @@
     <col width="9" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>결산 조정 명세 (줄무늬 없음)</t>
+          <t>07_줄무늬OFF</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -1812,11 +1802,10 @@
     <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>체크리스트</t>
+          <t>08_2열목록</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -1884,15 +1873,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>주요 가정 · 입력/연결 셀</t>
+          <t>09_입력연결셀</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
